--- a/data/fall2425_course_info.xlsx
+++ b/data/fall2425_course_info.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD9869A2-A323-401B-9E1F-2EA336B7E0BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59235B0F-C858-40FE-87E2-65308CBF8266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="5940" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1711,7 +1711,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1E0F4194-B6AA-41D9-8C03-142586E7DC79}" name="Table2" displayName="Table2" ref="A1:O444" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A1:O444" xr:uid="{1E0F4194-B6AA-41D9-8C03-142586E7DC79}"/>
+  <autoFilter ref="A1:O444" xr:uid="{1E0F4194-B6AA-41D9-8C03-142586E7DC79}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Bilgisayar Mühendisliği  (İngilizce)"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{11E739C3-C453-428E-9655-EA8F32139142}" name="DepartmentName" dataDxfId="14"/>
     <tableColumn id="2" xr3:uid="{664E9CFD-31B9-40AF-B403-1D5C124DEE5E}" name="CourseName" dataDxfId="13"/>
@@ -2108,7 +2114,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>41</v>
       </c>
@@ -2155,7 +2161,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>41</v>
       </c>
@@ -2202,7 +2208,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -2249,7 +2255,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>41</v>
       </c>
@@ -2390,7 +2396,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
@@ -2437,7 +2443,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>46</v>
       </c>
@@ -2484,7 +2490,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>46</v>
       </c>
@@ -2578,7 +2584,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>34</v>
       </c>
@@ -2625,7 +2631,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>24</v>
       </c>
@@ -2672,7 +2678,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
@@ -2719,7 +2725,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>32</v>
       </c>
@@ -2766,7 +2772,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>41</v>
       </c>
@@ -2813,7 +2819,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>41</v>
       </c>
@@ -2860,7 +2866,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>41</v>
       </c>
@@ -2907,7 +2913,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>46</v>
       </c>
@@ -2954,7 +2960,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>34</v>
       </c>
@@ -3001,7 +3007,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>34</v>
       </c>
@@ -3048,7 +3054,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>34</v>
       </c>
@@ -3095,7 +3101,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
@@ -3142,7 +3148,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
@@ -3189,7 +3195,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>21</v>
       </c>
@@ -3236,7 +3242,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>24</v>
       </c>
@@ -3283,7 +3289,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>32</v>
       </c>
@@ -3330,7 +3336,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>34</v>
       </c>
@@ -3377,7 +3383,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>34</v>
       </c>
@@ -3424,7 +3430,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>46</v>
       </c>
@@ -3471,7 +3477,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>24</v>
       </c>
@@ -3518,7 +3524,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
@@ -3565,7 +3571,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>41</v>
       </c>
@@ -3612,7 +3618,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>21</v>
       </c>
@@ -3659,7 +3665,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>46</v>
       </c>
@@ -3706,7 +3712,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>15</v>
       </c>
@@ -3753,7 +3759,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>15</v>
       </c>
@@ -3800,7 +3806,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>15</v>
       </c>
@@ -3847,7 +3853,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>46</v>
       </c>
@@ -3894,7 +3900,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>15</v>
       </c>
@@ -3941,7 +3947,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>15</v>
       </c>
@@ -3988,7 +3994,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>15</v>
       </c>
@@ -4035,7 +4041,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>15</v>
       </c>
@@ -4082,7 +4088,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>15</v>
       </c>
@@ -4129,7 +4135,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>15</v>
       </c>
@@ -4176,7 +4182,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>15</v>
       </c>
@@ -4223,7 +4229,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>15</v>
       </c>
@@ -4270,7 +4276,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>15</v>
       </c>
@@ -4317,7 +4323,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>15</v>
       </c>
@@ -4364,7 +4370,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>15</v>
       </c>
@@ -4411,7 +4417,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>21</v>
       </c>
@@ -4458,7 +4464,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>21</v>
       </c>
@@ -4505,7 +4511,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>21</v>
       </c>
@@ -4552,7 +4558,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>21</v>
       </c>
@@ -4599,7 +4605,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>21</v>
       </c>
@@ -4646,7 +4652,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>21</v>
       </c>
@@ -4693,7 +4699,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>21</v>
       </c>
@@ -4740,7 +4746,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>21</v>
       </c>
@@ -4787,7 +4793,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>21</v>
       </c>
@@ -4834,7 +4840,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>21</v>
       </c>
@@ -4881,7 +4887,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>21</v>
       </c>
@@ -4928,7 +4934,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>21</v>
       </c>
@@ -4975,7 +4981,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>21</v>
       </c>
@@ -5022,7 +5028,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>15</v>
       </c>
@@ -5069,7 +5075,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>15</v>
       </c>
@@ -5116,7 +5122,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>15</v>
       </c>
@@ -5163,7 +5169,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>15</v>
       </c>
@@ -5210,7 +5216,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>15</v>
       </c>
@@ -5257,7 +5263,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>15</v>
       </c>
@@ -5304,7 +5310,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>15</v>
       </c>
@@ -5351,7 +5357,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>34</v>
       </c>
@@ -5398,7 +5404,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>15</v>
       </c>
@@ -5445,7 +5451,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>46</v>
       </c>
@@ -5492,7 +5498,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>24</v>
       </c>
@@ -5539,7 +5545,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>32</v>
       </c>
@@ -5586,7 +5592,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>34</v>
       </c>
@@ -5633,7 +5639,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>34</v>
       </c>
@@ -5680,7 +5686,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>24</v>
       </c>
@@ -5727,7 +5733,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>32</v>
       </c>
@@ -5774,7 +5780,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>41</v>
       </c>
@@ -5821,7 +5827,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>41</v>
       </c>
@@ -5868,7 +5874,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>41</v>
       </c>
@@ -6197,7 +6203,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>24</v>
       </c>
@@ -6244,7 +6250,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>41</v>
       </c>
@@ -6291,7 +6297,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>34</v>
       </c>
@@ -6385,7 +6391,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>24</v>
       </c>
@@ -6432,7 +6438,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>32</v>
       </c>
@@ -6479,7 +6485,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>24</v>
       </c>
@@ -6526,7 +6532,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>24</v>
       </c>
@@ -6573,7 +6579,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>32</v>
       </c>
@@ -6620,7 +6626,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>32</v>
       </c>
@@ -6667,7 +6673,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>21</v>
       </c>
@@ -6714,7 +6720,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>41</v>
       </c>
@@ -6761,7 +6767,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>46</v>
       </c>
@@ -6808,7 +6814,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>34</v>
       </c>
@@ -6855,7 +6861,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>34</v>
       </c>
@@ -6902,7 +6908,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>24</v>
       </c>
@@ -6949,7 +6955,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>32</v>
       </c>
@@ -7090,7 +7096,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>34</v>
       </c>
@@ -7137,7 +7143,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>21</v>
       </c>
@@ -7231,7 +7237,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>46</v>
       </c>
@@ -7278,7 +7284,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>24</v>
       </c>
@@ -7325,7 +7331,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>24</v>
       </c>
@@ -7372,7 +7378,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
         <v>32</v>
       </c>
@@ -7419,7 +7425,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>32</v>
       </c>
@@ -7466,7 +7472,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>24</v>
       </c>
@@ -7513,7 +7519,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>32</v>
       </c>
@@ -7560,7 +7566,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>32</v>
       </c>
@@ -7607,7 +7613,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>24</v>
       </c>
@@ -7654,7 +7660,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>24</v>
       </c>
@@ -7701,7 +7707,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
         <v>24</v>
       </c>
@@ -7748,7 +7754,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>32</v>
       </c>
@@ -7795,7 +7801,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>32</v>
       </c>
@@ -7842,7 +7848,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
         <v>24</v>
       </c>
@@ -7889,7 +7895,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
         <v>24</v>
       </c>
@@ -7936,7 +7942,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
         <v>32</v>
       </c>
@@ -7983,7 +7989,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>32</v>
       </c>
@@ -8030,7 +8036,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
         <v>24</v>
       </c>
@@ -8077,7 +8083,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>32</v>
       </c>
@@ -8124,7 +8130,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
         <v>24</v>
       </c>
@@ -8171,7 +8177,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
         <v>24</v>
       </c>
@@ -8218,7 +8224,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>24</v>
       </c>
@@ -8265,7 +8271,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>32</v>
       </c>
@@ -8312,7 +8318,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>46</v>
       </c>
@@ -8453,7 +8459,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>46</v>
       </c>
@@ -8500,7 +8506,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
         <v>46</v>
       </c>
@@ -8594,7 +8600,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>41</v>
       </c>
@@ -8641,7 +8647,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
         <v>21</v>
       </c>
@@ -8688,7 +8694,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
         <v>46</v>
       </c>
@@ -8735,7 +8741,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
         <v>46</v>
       </c>
@@ -8782,7 +8788,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
         <v>21</v>
       </c>
@@ -8829,7 +8835,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
         <v>34</v>
       </c>
@@ -8876,7 +8882,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
         <v>46</v>
       </c>
@@ -8923,7 +8929,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
         <v>46</v>
       </c>
@@ -8970,7 +8976,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
         <v>46</v>
       </c>
@@ -9064,7 +9070,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
         <v>24</v>
       </c>
@@ -9111,7 +9117,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
         <v>32</v>
       </c>
@@ -9158,7 +9164,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
         <v>32</v>
       </c>
@@ -9205,7 +9211,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
         <v>24</v>
       </c>
@@ -9299,7 +9305,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
         <v>41</v>
       </c>
@@ -9534,7 +9540,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
         <v>21</v>
       </c>
@@ -9581,7 +9587,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
         <v>34</v>
       </c>
@@ -9628,7 +9634,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
         <v>46</v>
       </c>
@@ -9675,7 +9681,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
         <v>46</v>
       </c>
@@ -9722,7 +9728,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
         <v>41</v>
       </c>
@@ -9769,7 +9775,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
         <v>46</v>
       </c>
@@ -9816,7 +9822,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
         <v>46</v>
       </c>
@@ -9863,7 +9869,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
         <v>46</v>
       </c>
@@ -9910,7 +9916,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
         <v>46</v>
       </c>
@@ -9957,7 +9963,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
         <v>46</v>
       </c>
@@ -10004,7 +10010,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" s="1" t="s">
         <v>46</v>
       </c>
@@ -10051,7 +10057,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
         <v>46</v>
       </c>
@@ -10098,7 +10104,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
         <v>46</v>
       </c>
@@ -10145,7 +10151,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
         <v>46</v>
       </c>
@@ -10192,7 +10198,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" s="1" t="s">
         <v>46</v>
       </c>
@@ -10239,7 +10245,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" s="1" t="s">
         <v>46</v>
       </c>
@@ -10286,7 +10292,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" s="1" t="s">
         <v>21</v>
       </c>
@@ -10333,7 +10339,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" s="1" t="s">
         <v>15</v>
       </c>
@@ -10380,7 +10386,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
         <v>24</v>
       </c>
@@ -10427,7 +10433,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" s="1" t="s">
         <v>32</v>
       </c>
@@ -10474,7 +10480,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
         <v>32</v>
       </c>
@@ -10521,7 +10527,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" s="1" t="s">
         <v>24</v>
       </c>
@@ -10568,7 +10574,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" s="1" t="s">
         <v>32</v>
       </c>
@@ -10615,7 +10621,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" s="1" t="s">
         <v>32</v>
       </c>
@@ -10662,7 +10668,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
         <v>24</v>
       </c>
@@ -10709,7 +10715,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" s="1" t="s">
         <v>24</v>
       </c>
@@ -10756,7 +10762,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" s="1" t="s">
         <v>24</v>
       </c>
@@ -10803,7 +10809,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" s="1" t="s">
         <v>24</v>
       </c>
@@ -10850,7 +10856,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" s="1" t="s">
         <v>34</v>
       </c>
@@ -10897,7 +10903,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" s="1" t="s">
         <v>21</v>
       </c>
@@ -10944,7 +10950,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" s="1" t="s">
         <v>34</v>
       </c>
@@ -10991,7 +10997,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" s="1" t="s">
         <v>21</v>
       </c>
@@ -11038,7 +11044,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" s="1" t="s">
         <v>24</v>
       </c>
@@ -11085,7 +11091,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" s="1" t="s">
         <v>32</v>
       </c>
@@ -11132,7 +11138,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" s="1" t="s">
         <v>24</v>
       </c>
@@ -11179,7 +11185,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" s="1" t="s">
         <v>21</v>
       </c>
@@ -11226,7 +11232,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" s="1" t="s">
         <v>24</v>
       </c>
@@ -11273,7 +11279,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" s="1" t="s">
         <v>21</v>
       </c>
@@ -11320,7 +11326,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" s="1" t="s">
         <v>46</v>
       </c>
@@ -11367,7 +11373,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" s="1" t="s">
         <v>34</v>
       </c>
@@ -11414,7 +11420,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" s="1" t="s">
         <v>34</v>
       </c>
@@ -11461,7 +11467,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" s="1" t="s">
         <v>443</v>
       </c>
@@ -11602,7 +11608,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" s="1" t="s">
         <v>32</v>
       </c>
@@ -11649,7 +11655,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" s="1" t="s">
         <v>24</v>
       </c>
@@ -11696,7 +11702,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" s="1" t="s">
         <v>41</v>
       </c>
@@ -11790,7 +11796,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" s="1" t="s">
         <v>24</v>
       </c>
@@ -11837,7 +11843,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" s="1" t="s">
         <v>32</v>
       </c>
@@ -11931,7 +11937,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" s="1" t="s">
         <v>15</v>
       </c>
@@ -11978,7 +11984,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" s="1" t="s">
         <v>24</v>
       </c>
@@ -12025,7 +12031,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" s="1" t="s">
         <v>46</v>
       </c>
@@ -12072,7 +12078,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" s="1" t="s">
         <v>21</v>
       </c>
@@ -12119,7 +12125,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" s="1" t="s">
         <v>15</v>
       </c>
@@ -12166,7 +12172,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" s="1" t="s">
         <v>15</v>
       </c>
@@ -12213,7 +12219,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" s="1" t="s">
         <v>15</v>
       </c>
@@ -12260,7 +12266,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" s="1" t="s">
         <v>21</v>
       </c>
@@ -12307,7 +12313,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" s="1" t="s">
         <v>21</v>
       </c>
@@ -12354,7 +12360,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" s="1" t="s">
         <v>46</v>
       </c>
@@ -12401,7 +12407,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" s="1" t="s">
         <v>34</v>
       </c>
@@ -12448,7 +12454,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" s="1" t="s">
         <v>34</v>
       </c>
@@ -12495,7 +12501,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" s="1" t="s">
         <v>24</v>
       </c>
@@ -12542,7 +12548,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" s="1" t="s">
         <v>32</v>
       </c>
@@ -12589,7 +12595,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" s="1" t="s">
         <v>21</v>
       </c>
@@ -12636,7 +12642,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" s="1" t="s">
         <v>15</v>
       </c>
@@ -12683,7 +12689,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" s="1" t="s">
         <v>41</v>
       </c>
@@ -12730,7 +12736,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" s="1" t="s">
         <v>41</v>
       </c>
@@ -12777,7 +12783,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" s="1" t="s">
         <v>15</v>
       </c>
@@ -12824,7 +12830,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" s="1" t="s">
         <v>21</v>
       </c>
@@ -12871,7 +12877,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" s="1" t="s">
         <v>41</v>
       </c>
@@ -12918,7 +12924,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" s="1" t="s">
         <v>15</v>
       </c>
@@ -12965,7 +12971,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" s="1" t="s">
         <v>21</v>
       </c>
@@ -13012,7 +13018,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" s="1" t="s">
         <v>21</v>
       </c>
@@ -13059,7 +13065,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" s="1" t="s">
         <v>15</v>
       </c>
@@ -13106,7 +13112,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" s="1" t="s">
         <v>46</v>
       </c>
@@ -13153,7 +13159,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" s="1" t="s">
         <v>46</v>
       </c>
@@ -13200,7 +13206,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" s="1" t="s">
         <v>46</v>
       </c>
@@ -13247,7 +13253,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" s="1" t="s">
         <v>15</v>
       </c>
@@ -13294,7 +13300,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" s="1" t="s">
         <v>21</v>
       </c>
@@ -13341,7 +13347,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" s="1" t="s">
         <v>21</v>
       </c>
@@ -13388,7 +13394,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" s="1" t="s">
         <v>21</v>
       </c>
@@ -13435,7 +13441,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" s="1" t="s">
         <v>21</v>
       </c>
@@ -13482,7 +13488,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" s="1" t="s">
         <v>21</v>
       </c>
@@ -13529,7 +13535,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" s="1" t="s">
         <v>21</v>
       </c>
@@ -13576,7 +13582,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" s="1" t="s">
         <v>21</v>
       </c>
@@ -13623,7 +13629,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" s="1" t="s">
         <v>21</v>
       </c>
@@ -13670,7 +13676,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" s="1" t="s">
         <v>21</v>
       </c>
@@ -13717,7 +13723,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" s="1" t="s">
         <v>21</v>
       </c>
@@ -13764,7 +13770,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" s="1" t="s">
         <v>21</v>
       </c>
@@ -13811,7 +13817,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" s="1" t="s">
         <v>21</v>
       </c>
@@ -13858,7 +13864,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" s="1" t="s">
         <v>21</v>
       </c>
@@ -13905,7 +13911,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" s="1" t="s">
         <v>21</v>
       </c>
@@ -13952,7 +13958,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" s="1" t="s">
         <v>21</v>
       </c>
@@ -13999,7 +14005,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" s="1" t="s">
         <v>21</v>
       </c>
@@ -14046,7 +14052,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" s="1" t="s">
         <v>21</v>
       </c>
@@ -14093,7 +14099,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" s="1" t="s">
         <v>21</v>
       </c>
@@ -14140,7 +14146,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" s="1" t="s">
         <v>21</v>
       </c>
@@ -14187,7 +14193,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" s="1" t="s">
         <v>34</v>
       </c>
@@ -14234,7 +14240,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" s="1" t="s">
         <v>21</v>
       </c>
@@ -14281,7 +14287,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" s="1" t="s">
         <v>21</v>
       </c>
@@ -14328,7 +14334,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" s="1" t="s">
         <v>32</v>
       </c>
@@ -14375,7 +14381,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" s="1" t="s">
         <v>24</v>
       </c>
@@ -14422,7 +14428,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" s="1" t="s">
         <v>24</v>
       </c>
@@ -14469,7 +14475,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" s="1" t="s">
         <v>32</v>
       </c>
@@ -14516,7 +14522,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" s="1" t="s">
         <v>34</v>
       </c>
@@ -14563,7 +14569,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" s="1" t="s">
         <v>46</v>
       </c>
@@ -14610,7 +14616,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" s="1" t="s">
         <v>21</v>
       </c>
@@ -14657,7 +14663,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" s="1" t="s">
         <v>32</v>
       </c>
@@ -14751,7 +14757,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" s="1" t="s">
         <v>24</v>
       </c>
@@ -14798,7 +14804,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" s="1" t="s">
         <v>21</v>
       </c>
@@ -14845,7 +14851,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" s="1" t="s">
         <v>41</v>
       </c>
@@ -14892,7 +14898,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" s="1" t="s">
         <v>21</v>
       </c>
@@ -14939,7 +14945,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" s="1" t="s">
         <v>46</v>
       </c>
@@ -14986,7 +14992,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" s="1" t="s">
         <v>46</v>
       </c>
@@ -15033,7 +15039,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" s="1" t="s">
         <v>24</v>
       </c>
@@ -15080,7 +15086,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" s="1" t="s">
         <v>24</v>
       </c>
@@ -15127,7 +15133,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" s="1" t="s">
         <v>32</v>
       </c>
@@ -15174,7 +15180,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" s="1" t="s">
         <v>32</v>
       </c>
@@ -15221,7 +15227,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" s="1" t="s">
         <v>32</v>
       </c>
@@ -15268,7 +15274,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" s="1" t="s">
         <v>24</v>
       </c>
@@ -15315,7 +15321,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" s="1" t="s">
         <v>24</v>
       </c>
@@ -15362,7 +15368,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" s="1" t="s">
         <v>24</v>
       </c>
@@ -15409,7 +15415,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" s="1" t="s">
         <v>32</v>
       </c>
@@ -15456,7 +15462,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" s="1" t="s">
         <v>32</v>
       </c>
@@ -15503,7 +15509,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" s="1" t="s">
         <v>32</v>
       </c>
@@ -15550,7 +15556,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" s="1" t="s">
         <v>24</v>
       </c>
@@ -15597,7 +15603,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" s="1" t="s">
         <v>24</v>
       </c>
@@ -15644,7 +15650,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" s="1" t="s">
         <v>24</v>
       </c>
@@ -15691,7 +15697,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" s="1" t="s">
         <v>32</v>
       </c>
@@ -15738,7 +15744,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" s="1" t="s">
         <v>24</v>
       </c>
@@ -15785,7 +15791,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" s="1" t="s">
         <v>32</v>
       </c>
@@ -15926,7 +15932,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" s="1" t="s">
         <v>46</v>
       </c>
@@ -15973,7 +15979,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" s="1" t="s">
         <v>46</v>
       </c>
@@ -16020,7 +16026,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" s="1" t="s">
         <v>15</v>
       </c>
@@ -16067,7 +16073,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" s="1" t="s">
         <v>24</v>
       </c>
@@ -16114,7 +16120,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" s="1" t="s">
         <v>32</v>
       </c>
@@ -16161,7 +16167,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" s="1" t="s">
         <v>24</v>
       </c>
@@ -16208,7 +16214,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" s="1" t="s">
         <v>15</v>
       </c>
@@ -16255,7 +16261,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" s="1" t="s">
         <v>34</v>
       </c>
@@ -16302,7 +16308,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" s="1" t="s">
         <v>21</v>
       </c>
@@ -16443,7 +16449,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="308" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" s="1" t="s">
         <v>46</v>
       </c>
@@ -16537,7 +16543,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="310" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" s="1" t="s">
         <v>34</v>
       </c>
@@ -16584,7 +16590,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="311" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" s="1" t="s">
         <v>21</v>
       </c>
@@ -16631,7 +16637,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" s="1" t="s">
         <v>34</v>
       </c>
@@ -16678,7 +16684,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="313" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" s="1" t="s">
         <v>21</v>
       </c>
@@ -16725,7 +16731,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="314" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" s="1" t="s">
         <v>32</v>
       </c>
@@ -16772,7 +16778,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="315" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" s="1" t="s">
         <v>24</v>
       </c>
@@ -16819,7 +16825,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="316" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" s="1" t="s">
         <v>15</v>
       </c>
@@ -16866,7 +16872,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="317" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" s="1" t="s">
         <v>41</v>
       </c>
@@ -16960,7 +16966,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="319" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" s="1" t="s">
         <v>32</v>
       </c>
@@ -17007,7 +17013,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="320" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" s="1" t="s">
         <v>41</v>
       </c>
@@ -17054,7 +17060,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="321" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" s="1" t="s">
         <v>32</v>
       </c>
@@ -17195,7 +17201,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="324" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" s="1" t="s">
         <v>24</v>
       </c>
@@ -17242,7 +17248,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="325" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" s="1" t="s">
         <v>24</v>
       </c>
@@ -17289,7 +17295,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="326" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" s="1" t="s">
         <v>32</v>
       </c>
@@ -17336,7 +17342,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="327" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" s="1" t="s">
         <v>32</v>
       </c>
@@ -17430,7 +17436,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="329" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" s="1" t="s">
         <v>24</v>
       </c>
@@ -17477,7 +17483,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="330" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" s="1" t="s">
         <v>32</v>
       </c>
@@ -17524,7 +17530,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="331" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" s="1" t="s">
         <v>21</v>
       </c>
@@ -17571,7 +17577,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="332" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" s="1" t="s">
         <v>21</v>
       </c>
@@ -17618,7 +17624,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="333" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" s="1" t="s">
         <v>21</v>
       </c>
@@ -17665,7 +17671,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="334" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" s="1" t="s">
         <v>34</v>
       </c>
@@ -17712,7 +17718,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="335" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335" s="1" t="s">
         <v>21</v>
       </c>
@@ -17759,7 +17765,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="336" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336" s="1" t="s">
         <v>15</v>
       </c>
@@ -17806,7 +17812,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="337" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337" s="1" t="s">
         <v>15</v>
       </c>
@@ -17853,7 +17859,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="338" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" s="1" t="s">
         <v>46</v>
       </c>
@@ -17900,7 +17906,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="339" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339" s="1" t="s">
         <v>41</v>
       </c>
@@ -17947,7 +17953,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="340" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" s="1" t="s">
         <v>41</v>
       </c>
@@ -17994,7 +18000,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" s="1" t="s">
         <v>41</v>
       </c>
@@ -18041,7 +18047,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="342" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" s="1" t="s">
         <v>41</v>
       </c>
@@ -18088,7 +18094,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" s="1" t="s">
         <v>41</v>
       </c>
@@ -18135,7 +18141,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="344" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" s="1" t="s">
         <v>41</v>
       </c>
@@ -18182,7 +18188,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="345" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" s="1" t="s">
         <v>41</v>
       </c>
@@ -18229,7 +18235,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="346" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346" s="1" t="s">
         <v>46</v>
       </c>
@@ -18276,7 +18282,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="347" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" s="1" t="s">
         <v>46</v>
       </c>
@@ -18323,7 +18329,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="348" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" s="1" t="s">
         <v>46</v>
       </c>
@@ -18370,7 +18376,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="349" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349" s="1" t="s">
         <v>46</v>
       </c>
@@ -18417,7 +18423,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="350" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A350" s="1" t="s">
         <v>46</v>
       </c>
@@ -18464,7 +18470,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="351" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" s="1" t="s">
         <v>46</v>
       </c>
@@ -18511,7 +18517,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="352" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" s="1" t="s">
         <v>46</v>
       </c>
@@ -18558,7 +18564,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="353" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" s="1" t="s">
         <v>46</v>
       </c>
@@ -18605,7 +18611,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="354" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" s="1" t="s">
         <v>41</v>
       </c>
@@ -18652,7 +18658,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="355" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" s="1" t="s">
         <v>46</v>
       </c>
@@ -18699,7 +18705,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="356" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A356" s="1" t="s">
         <v>46</v>
       </c>
@@ -18746,7 +18752,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="357" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" s="1" t="s">
         <v>46</v>
       </c>
@@ -18793,7 +18799,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="358" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358" s="1" t="s">
         <v>41</v>
       </c>
@@ -18840,7 +18846,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="359" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359" s="1" t="s">
         <v>41</v>
       </c>
@@ -18887,7 +18893,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="360" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" s="1" t="s">
         <v>46</v>
       </c>
@@ -18934,7 +18940,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="361" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" s="1" t="s">
         <v>41</v>
       </c>
@@ -18981,7 +18987,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="362" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" s="1" t="s">
         <v>46</v>
       </c>
@@ -19028,7 +19034,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="363" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363" s="1" t="s">
         <v>41</v>
       </c>
@@ -19075,7 +19081,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="364" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364" s="1" t="s">
         <v>41</v>
       </c>
@@ -19122,7 +19128,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="365" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365" s="1" t="s">
         <v>34</v>
       </c>
@@ -19169,7 +19175,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="366" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" s="1" t="s">
         <v>34</v>
       </c>
@@ -19216,7 +19222,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="367" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367" s="1" t="s">
         <v>34</v>
       </c>
@@ -19263,7 +19269,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="368" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368" s="1" t="s">
         <v>34</v>
       </c>
@@ -19310,7 +19316,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="369" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369" s="1" t="s">
         <v>34</v>
       </c>
@@ -19357,7 +19363,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="370" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370" s="1" t="s">
         <v>34</v>
       </c>
@@ -19404,7 +19410,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="371" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A371" s="1" t="s">
         <v>34</v>
       </c>
@@ -19451,7 +19457,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="372" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372" s="1" t="s">
         <v>34</v>
       </c>
@@ -19498,7 +19504,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="373" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A373" s="1" t="s">
         <v>34</v>
       </c>
@@ -19545,7 +19551,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="374" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374" s="1" t="s">
         <v>34</v>
       </c>
@@ -19592,7 +19598,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="375" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A375" s="1" t="s">
         <v>34</v>
       </c>
@@ -19639,7 +19645,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="376" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" s="1" t="s">
         <v>34</v>
       </c>
@@ -19686,7 +19692,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="377" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377" s="1" t="s">
         <v>34</v>
       </c>
@@ -19733,7 +19739,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="378" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A378" s="1" t="s">
         <v>34</v>
       </c>
@@ -19780,7 +19786,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="379" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A379" s="1" t="s">
         <v>34</v>
       </c>
@@ -20250,7 +20256,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="389" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A389" s="1" t="s">
         <v>32</v>
       </c>
@@ -20297,7 +20303,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="390" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A390" s="1" t="s">
         <v>24</v>
       </c>
@@ -20344,7 +20350,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="391" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A391" s="1" t="s">
         <v>21</v>
       </c>
@@ -20391,7 +20397,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="392" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A392" s="1" t="s">
         <v>21</v>
       </c>
@@ -20438,7 +20444,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="393" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A393" s="1" t="s">
         <v>15</v>
       </c>
@@ -20532,7 +20538,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="395" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A395" s="1" t="s">
         <v>41</v>
       </c>
@@ -20579,7 +20585,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="396" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A396" s="1" t="s">
         <v>41</v>
       </c>
@@ -20626,7 +20632,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="397" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A397" s="1" t="s">
         <v>34</v>
       </c>
@@ -20673,7 +20679,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="398" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A398" s="1" t="s">
         <v>46</v>
       </c>
@@ -20720,7 +20726,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="399" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A399" s="1" t="s">
         <v>21</v>
       </c>
@@ -20767,7 +20773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="400" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A400" s="1" t="s">
         <v>21</v>
       </c>
@@ -20814,7 +20820,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="401" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A401" s="1" t="s">
         <v>41</v>
       </c>
@@ -20861,7 +20867,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="402" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A402" s="1" t="s">
         <v>46</v>
       </c>
@@ -20908,7 +20914,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="403" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A403" s="1" t="s">
         <v>46</v>
       </c>
@@ -20955,7 +20961,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="404" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A404" s="1" t="s">
         <v>21</v>
       </c>
@@ -21002,7 +21008,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="405" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A405" s="1" t="s">
         <v>21</v>
       </c>
@@ -21049,7 +21055,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="406" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A406" s="1" t="s">
         <v>41</v>
       </c>
@@ -21096,7 +21102,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="407" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A407" s="1" t="s">
         <v>21</v>
       </c>
@@ -21143,7 +21149,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="408" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A408" s="1" t="s">
         <v>21</v>
       </c>
@@ -21190,7 +21196,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="409" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A409" s="1" t="s">
         <v>34</v>
       </c>
@@ -21237,7 +21243,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="410" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A410" s="1" t="s">
         <v>34</v>
       </c>
@@ -21284,7 +21290,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="411" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A411" s="1" t="s">
         <v>21</v>
       </c>
@@ -21331,7 +21337,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="412" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A412" s="1" t="s">
         <v>46</v>
       </c>
@@ -21378,7 +21384,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="413" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A413" s="1" t="s">
         <v>21</v>
       </c>
@@ -21425,7 +21431,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="414" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A414" s="1" t="s">
         <v>15</v>
       </c>
@@ -21472,7 +21478,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="415" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A415" s="1" t="s">
         <v>46</v>
       </c>
@@ -21519,7 +21525,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="416" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A416" s="1" t="s">
         <v>21</v>
       </c>
@@ -21566,7 +21572,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="417" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A417" s="1" t="s">
         <v>34</v>
       </c>
@@ -21613,7 +21619,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="418" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A418" s="1" t="s">
         <v>46</v>
       </c>
@@ -21660,7 +21666,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="419" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A419" s="1" t="s">
         <v>41</v>
       </c>
@@ -21707,7 +21713,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="420" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A420" s="1" t="s">
         <v>21</v>
       </c>
@@ -21754,7 +21760,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="421" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A421" s="1" t="s">
         <v>15</v>
       </c>
@@ -21801,7 +21807,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="422" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A422" s="1" t="s">
         <v>41</v>
       </c>
@@ -21848,7 +21854,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="423" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A423" s="1" t="s">
         <v>21</v>
       </c>
@@ -21895,7 +21901,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="424" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A424" s="1" t="s">
         <v>21</v>
       </c>
@@ -21942,7 +21948,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="425" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A425" s="1" t="s">
         <v>24</v>
       </c>
@@ -21989,7 +21995,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="426" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A426" s="1" t="s">
         <v>46</v>
       </c>
@@ -22036,7 +22042,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="427" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A427" s="1" t="s">
         <v>34</v>
       </c>
@@ -22083,7 +22089,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="428" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A428" s="1" t="s">
         <v>32</v>
       </c>
@@ -22130,7 +22136,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="429" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A429" s="1" t="s">
         <v>41</v>
       </c>
@@ -22177,7 +22183,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="430" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A430" s="1" t="s">
         <v>34</v>
       </c>
@@ -22224,7 +22230,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="431" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A431" s="1" t="s">
         <v>15</v>
       </c>
@@ -22271,7 +22277,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="432" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A432" s="1" t="s">
         <v>15</v>
       </c>
@@ -22365,7 +22371,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="434" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A434" s="1" t="s">
         <v>21</v>
       </c>
@@ -22412,7 +22418,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="435" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A435" s="1" t="s">
         <v>34</v>
       </c>
@@ -22459,7 +22465,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="436" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A436" s="1" t="s">
         <v>34</v>
       </c>
@@ -22506,7 +22512,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="437" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A437" s="1" t="s">
         <v>34</v>
       </c>
@@ -22553,7 +22559,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="438" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A438" s="1" t="s">
         <v>34</v>
       </c>
@@ -22600,7 +22606,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="439" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A439" s="1" t="s">
         <v>34</v>
       </c>
@@ -22647,7 +22653,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="440" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A440" s="1" t="s">
         <v>15</v>
       </c>
@@ -22694,7 +22700,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="441" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A441" s="1" t="s">
         <v>32</v>
       </c>
@@ -22741,7 +22747,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="442" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A442" s="1" t="s">
         <v>21</v>
       </c>
@@ -22788,7 +22794,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="443" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A443" s="1" t="s">
         <v>24</v>
       </c>
@@ -22835,7 +22841,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="444" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A444" s="1" t="s">
         <v>34</v>
       </c>
